--- a/dsa_py/SortingAnalysis.xlsx
+++ b/dsa_py/SortingAnalysis.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
         <v>45</v>
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>45</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D5" t="n">
         <v>190</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D7" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="D8" t="n">
         <v>435</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>435</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>230</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D11" t="n">
         <v>780</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
         <v>780</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D13" t="n">
         <v>398</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="D14" t="n">
         <v>1225</v>
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="D16" t="n">
-        <v>692</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>953</v>
+        <v>998</v>
       </c>
       <c r="D17" t="n">
         <v>1770</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>1770</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>953</v>
+        <v>998</v>
       </c>
       <c r="D19" t="n">
-        <v>1007</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D20" t="n">
         <v>2415</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D22" t="n">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="23">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1375</v>
+        <v>1464</v>
       </c>
       <c r="D23" t="n">
         <v>3160</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D24" t="n">
         <v>3160</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1375</v>
+        <v>1464</v>
       </c>
       <c r="D25" t="n">
-        <v>1451</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="26">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2252</v>
+        <v>2306</v>
       </c>
       <c r="D26" t="n">
         <v>4005</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D27" t="n">
         <v>4005</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2252</v>
+        <v>2306</v>
       </c>
       <c r="D28" t="n">
-        <v>2339</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="29">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2464</v>
+        <v>2185</v>
       </c>
       <c r="D29" t="n">
         <v>4950</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D30" t="n">
         <v>4950</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2464</v>
+        <v>2185</v>
       </c>
       <c r="D31" t="n">
-        <v>2556</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="32">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3176</v>
+        <v>3472</v>
       </c>
       <c r="D32" t="n">
         <v>5995</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3176</v>
+        <v>3472</v>
       </c>
       <c r="D34" t="n">
-        <v>3279</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="35">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3622</v>
+        <v>4148</v>
       </c>
       <c r="D35" t="n">
         <v>7140</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3622</v>
+        <v>4148</v>
       </c>
       <c r="D37" t="n">
-        <v>3738</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="38">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4893</v>
+        <v>3816</v>
       </c>
       <c r="D38" t="n">
         <v>8385</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D39" t="n">
         <v>8385</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4893</v>
+        <v>3816</v>
       </c>
       <c r="D40" t="n">
-        <v>5017</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="41">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5283</v>
+        <v>5128</v>
       </c>
       <c r="D41" t="n">
         <v>9730</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D42" t="n">
         <v>9730</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5283</v>
+        <v>5128</v>
       </c>
       <c r="D43" t="n">
-        <v>5419</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="44">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5569</v>
+        <v>5844</v>
       </c>
       <c r="D44" t="n">
         <v>11175</v>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D45" t="n">
         <v>11175</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5569</v>
+        <v>5844</v>
       </c>
       <c r="D46" t="n">
-        <v>5715</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="47">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7049</v>
+        <v>6677</v>
       </c>
       <c r="D47" t="n">
         <v>12720</v>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D48" t="n">
         <v>12720</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7049</v>
+        <v>6677</v>
       </c>
       <c r="D49" t="n">
-        <v>7199</v>
+        <v>6831</v>
       </c>
     </row>
     <row r="50">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7176</v>
+        <v>6915</v>
       </c>
       <c r="D50" t="n">
         <v>14365</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7176</v>
+        <v>6915</v>
       </c>
       <c r="D52" t="n">
-        <v>7338</v>
+        <v>7079</v>
       </c>
     </row>
     <row r="53">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8049</v>
+        <v>7752</v>
       </c>
       <c r="D53" t="n">
         <v>16110</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D54" t="n">
         <v>16110</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8049</v>
+        <v>7752</v>
       </c>
       <c r="D55" t="n">
-        <v>8223</v>
+        <v>7928</v>
       </c>
     </row>
     <row r="56">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9624</v>
+        <v>9320</v>
       </c>
       <c r="D56" t="n">
         <v>17955</v>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" t="n">
         <v>17955</v>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9624</v>
+        <v>9320</v>
       </c>
       <c r="D58" t="n">
-        <v>9807</v>
+        <v>9504</v>
       </c>
     </row>
     <row r="59">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10291</v>
+        <v>9900</v>
       </c>
       <c r="D59" t="n">
         <v>19900</v>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D60" t="n">
         <v>19900</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10291</v>
+        <v>9900</v>
       </c>
       <c r="D61" t="n">
-        <v>10481</v>
+        <v>10093</v>
       </c>
     </row>
     <row r="62">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11153</v>
+        <v>10627</v>
       </c>
       <c r="D62" t="n">
         <v>21945</v>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D63" t="n">
         <v>21945</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11153</v>
+        <v>10627</v>
       </c>
       <c r="D64" t="n">
-        <v>11352</v>
+        <v>10835</v>
       </c>
     </row>
     <row r="65">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12554</v>
+        <v>12430</v>
       </c>
       <c r="D65" t="n">
         <v>24090</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D66" t="n">
         <v>24090</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12554</v>
+        <v>12430</v>
       </c>
       <c r="D67" t="n">
-        <v>12765</v>
+        <v>12642</v>
       </c>
     </row>
     <row r="68">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13087</v>
+        <v>13808</v>
       </c>
       <c r="D68" t="n">
         <v>26335</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D69" t="n">
         <v>26335</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13087</v>
+        <v>13808</v>
       </c>
       <c r="D70" t="n">
-        <v>13310</v>
+        <v>14032</v>
       </c>
     </row>
     <row r="71">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>14122</v>
+        <v>13667</v>
       </c>
       <c r="D71" t="n">
         <v>28680</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D72" t="n">
         <v>28680</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14122</v>
+        <v>13667</v>
       </c>
       <c r="D73" t="n">
-        <v>14358</v>
+        <v>13905</v>
       </c>
     </row>
     <row r="74">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15421</v>
+        <v>15888</v>
       </c>
       <c r="D74" t="n">
         <v>31125</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D75" t="n">
         <v>31125</v>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15421</v>
+        <v>15888</v>
       </c>
       <c r="D76" t="n">
-        <v>15666</v>
+        <v>16131</v>
       </c>
     </row>
     <row r="77">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>16744</v>
+        <v>17061</v>
       </c>
       <c r="D77" t="n">
         <v>33670</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>16744</v>
+        <v>17061</v>
       </c>
       <c r="D79" t="n">
-        <v>16998</v>
+        <v>17312</v>
       </c>
     </row>
     <row r="80">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>18109</v>
+        <v>18182</v>
       </c>
       <c r="D80" t="n">
         <v>36315</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D81" t="n">
         <v>36315</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>18109</v>
+        <v>18182</v>
       </c>
       <c r="D82" t="n">
-        <v>18376</v>
+        <v>18446</v>
       </c>
     </row>
     <row r="83">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20740</v>
+        <v>20393</v>
       </c>
       <c r="D83" t="n">
         <v>39060</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D84" t="n">
         <v>39060</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>20740</v>
+        <v>20393</v>
       </c>
       <c r="D85" t="n">
-        <v>21016</v>
+        <v>20667</v>
       </c>
     </row>
     <row r="86">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>21501</v>
+        <v>20452</v>
       </c>
       <c r="D86" t="n">
         <v>41905</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D87" t="n">
         <v>41905</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>21501</v>
+        <v>20452</v>
       </c>
       <c r="D88" t="n">
-        <v>21784</v>
+        <v>20735</v>
       </c>
     </row>
     <row r="89">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>21811</v>
+        <v>20743</v>
       </c>
       <c r="D89" t="n">
         <v>44850</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D90" t="n">
         <v>44850</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>21811</v>
+        <v>20743</v>
       </c>
       <c r="D91" t="n">
-        <v>22107</v>
+        <v>21036</v>
       </c>
     </row>
     <row r="92">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>23186</v>
+        <v>24222</v>
       </c>
       <c r="D92" t="n">
         <v>47895</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D93" t="n">
         <v>47895</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>23186</v>
+        <v>24222</v>
       </c>
       <c r="D94" t="n">
-        <v>23489</v>
+        <v>24527</v>
       </c>
     </row>
     <row r="95">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>25325</v>
+        <v>24820</v>
       </c>
       <c r="D95" t="n">
         <v>51040</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D96" t="n">
         <v>51040</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>25325</v>
+        <v>24820</v>
       </c>
       <c r="D97" t="n">
-        <v>25640</v>
+        <v>25133</v>
       </c>
     </row>
     <row r="98">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>27947</v>
+        <v>28030</v>
       </c>
       <c r="D98" t="n">
         <v>54285</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D99" t="n">
         <v>54285</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>27947</v>
+        <v>28030</v>
       </c>
       <c r="D100" t="n">
-        <v>28267</v>
+        <v>28356</v>
       </c>
     </row>
     <row r="101">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>29791</v>
+        <v>27849</v>
       </c>
       <c r="D101" t="n">
         <v>57630</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D102" t="n">
         <v>57630</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>29791</v>
+        <v>27849</v>
       </c>
       <c r="D103" t="n">
-        <v>30124</v>
+        <v>28185</v>
       </c>
     </row>
     <row r="104">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>29583</v>
+        <v>31976</v>
       </c>
       <c r="D104" t="n">
         <v>61075</v>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D105" t="n">
         <v>61075</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>29583</v>
+        <v>31976</v>
       </c>
       <c r="D106" t="n">
-        <v>29925</v>
+        <v>32322</v>
       </c>
     </row>
     <row r="107">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>31280</v>
+        <v>30731</v>
       </c>
       <c r="D107" t="n">
         <v>64620</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D108" t="n">
         <v>64620</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>31280</v>
+        <v>30731</v>
       </c>
       <c r="D109" t="n">
-        <v>31634</v>
+        <v>31080</v>
       </c>
     </row>
     <row r="110">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>31986</v>
+        <v>35322</v>
       </c>
       <c r="D110" t="n">
         <v>68265</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D111" t="n">
         <v>68265</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>31986</v>
+        <v>35322</v>
       </c>
       <c r="D112" t="n">
-        <v>32347</v>
+        <v>35684</v>
       </c>
     </row>
     <row r="113">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>36706</v>
+        <v>36502</v>
       </c>
       <c r="D113" t="n">
         <v>72010</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D114" t="n">
         <v>72010</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>36706</v>
+        <v>36502</v>
       </c>
       <c r="D115" t="n">
-        <v>37082</v>
+        <v>36875</v>
       </c>
     </row>
     <row r="116">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>37916</v>
+        <v>36510</v>
       </c>
       <c r="D116" t="n">
         <v>75855</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D117" t="n">
         <v>75855</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>37916</v>
+        <v>36510</v>
       </c>
       <c r="D118" t="n">
-        <v>38295</v>
+        <v>36894</v>
       </c>
     </row>
     <row r="119">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>37430</v>
+        <v>40521</v>
       </c>
       <c r="D119" t="n">
         <v>79800</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D120" t="n">
         <v>79800</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>37430</v>
+        <v>40521</v>
       </c>
       <c r="D121" t="n">
-        <v>37823</v>
+        <v>40914</v>
       </c>
     </row>
     <row r="122">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>40726</v>
+        <v>44440</v>
       </c>
       <c r="D122" t="n">
         <v>83845</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D123" t="n">
         <v>83845</v>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>40726</v>
+        <v>44440</v>
       </c>
       <c r="D124" t="n">
-        <v>41130</v>
+        <v>44843</v>
       </c>
     </row>
     <row r="125">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>41794</v>
+        <v>45085</v>
       </c>
       <c r="D125" t="n">
         <v>87990</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D126" t="n">
         <v>87990</v>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>41794</v>
+        <v>45085</v>
       </c>
       <c r="D127" t="n">
-        <v>42206</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="128">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>43917</v>
+        <v>46441</v>
       </c>
       <c r="D128" t="n">
         <v>92235</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D129" t="n">
         <v>92235</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>43917</v>
+        <v>46441</v>
       </c>
       <c r="D130" t="n">
-        <v>44342</v>
+        <v>46864</v>
       </c>
     </row>
     <row r="131">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>50428</v>
+        <v>46745</v>
       </c>
       <c r="D131" t="n">
         <v>96580</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D132" t="n">
         <v>96580</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>50428</v>
+        <v>46745</v>
       </c>
       <c r="D133" t="n">
-        <v>50860</v>
+        <v>47178</v>
       </c>
     </row>
     <row r="134">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>51797</v>
+        <v>52711</v>
       </c>
       <c r="D134" t="n">
         <v>101025</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>51797</v>
+        <v>52711</v>
       </c>
       <c r="D136" t="n">
-        <v>52237</v>
+        <v>53151</v>
       </c>
     </row>
     <row r="137">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>53438</v>
+        <v>52042</v>
       </c>
       <c r="D137" t="n">
         <v>105570</v>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D138" t="n">
         <v>105570</v>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>53438</v>
+        <v>52042</v>
       </c>
       <c r="D139" t="n">
-        <v>53890</v>
+        <v>52495</v>
       </c>
     </row>
     <row r="140">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>58250</v>
+        <v>53737</v>
       </c>
       <c r="D140" t="n">
         <v>110215</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>58250</v>
+        <v>53737</v>
       </c>
       <c r="D142" t="n">
-        <v>58708</v>
+        <v>54203</v>
       </c>
     </row>
     <row r="143">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>59455</v>
+        <v>55629</v>
       </c>
       <c r="D143" t="n">
         <v>114960</v>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>59455</v>
+        <v>55629</v>
       </c>
       <c r="D145" t="n">
-        <v>59930</v>
+        <v>56104</v>
       </c>
     </row>
     <row r="146">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>61939</v>
+        <v>59708</v>
       </c>
       <c r="D146" t="n">
         <v>119805</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D147" t="n">
         <v>119805</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>61939</v>
+        <v>59708</v>
       </c>
       <c r="D148" t="n">
-        <v>62425</v>
+        <v>60193</v>
       </c>
     </row>
     <row r="149">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>62729</v>
+        <v>63190</v>
       </c>
       <c r="D149" t="n">
         <v>124750</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D150" t="n">
         <v>124750</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>62729</v>
+        <v>63190</v>
       </c>
       <c r="D151" t="n">
-        <v>63224</v>
+        <v>63682</v>
       </c>
     </row>
     <row r="152">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>67840</v>
+        <v>67043</v>
       </c>
       <c r="D152" t="n">
         <v>129795</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D153" t="n">
         <v>129795</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>67840</v>
+        <v>67043</v>
       </c>
       <c r="D154" t="n">
-        <v>68343</v>
+        <v>67545</v>
       </c>
     </row>
     <row r="155">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>68961</v>
+        <v>70385</v>
       </c>
       <c r="D155" t="n">
         <v>134940</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D156" t="n">
         <v>134940</v>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>68961</v>
+        <v>70385</v>
       </c>
       <c r="D157" t="n">
-        <v>69470</v>
+        <v>70896</v>
       </c>
     </row>
     <row r="158">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>71175</v>
+        <v>70192</v>
       </c>
       <c r="D158" t="n">
         <v>140185</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D159" t="n">
         <v>140185</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>71175</v>
+        <v>70192</v>
       </c>
       <c r="D160" t="n">
-        <v>71695</v>
+        <v>70714</v>
       </c>
     </row>
     <row r="161">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>70946</v>
+        <v>71701</v>
       </c>
       <c r="D161" t="n">
         <v>145530</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D162" t="n">
         <v>145530</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>70946</v>
+        <v>71701</v>
       </c>
       <c r="D163" t="n">
-        <v>71480</v>
+        <v>72235</v>
       </c>
     </row>
     <row r="164">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>77771</v>
+        <v>74967</v>
       </c>
       <c r="D164" t="n">
         <v>150975</v>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D165" t="n">
         <v>150975</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>77771</v>
+        <v>74967</v>
       </c>
       <c r="D166" t="n">
-        <v>78316</v>
+        <v>75508</v>
       </c>
     </row>
     <row r="167">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>81953</v>
+        <v>82562</v>
       </c>
       <c r="D167" t="n">
         <v>156520</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D168" t="n">
         <v>156520</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>81953</v>
+        <v>82562</v>
       </c>
       <c r="D169" t="n">
-        <v>82506</v>
+        <v>83113</v>
       </c>
     </row>
     <row r="170">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>82325</v>
+        <v>80489</v>
       </c>
       <c r="D170" t="n">
         <v>162165</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D171" t="n">
         <v>162165</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>82325</v>
+        <v>80489</v>
       </c>
       <c r="D172" t="n">
-        <v>82887</v>
+        <v>81055</v>
       </c>
     </row>
     <row r="173">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>83399</v>
+        <v>83392</v>
       </c>
       <c r="D173" t="n">
         <v>167910</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D174" t="n">
         <v>167910</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>83399</v>
+        <v>83392</v>
       </c>
       <c r="D175" t="n">
-        <v>83976</v>
+        <v>83967</v>
       </c>
     </row>
     <row r="176">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>86589</v>
+        <v>84767</v>
       </c>
       <c r="D176" t="n">
         <v>173755</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D177" t="n">
         <v>173755</v>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>86589</v>
+        <v>84767</v>
       </c>
       <c r="D178" t="n">
-        <v>87173</v>
+        <v>85354</v>
       </c>
     </row>
     <row r="179">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>90372</v>
+        <v>88724</v>
       </c>
       <c r="D179" t="n">
         <v>179700</v>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D180" t="n">
         <v>179700</v>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>90372</v>
+        <v>88724</v>
       </c>
       <c r="D181" t="n">
-        <v>90966</v>
+        <v>89321</v>
       </c>
     </row>
     <row r="182">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>95706</v>
+        <v>89804</v>
       </c>
       <c r="D182" t="n">
         <v>185745</v>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D183" t="n">
         <v>185745</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>95706</v>
+        <v>89804</v>
       </c>
       <c r="D184" t="n">
-        <v>96311</v>
+        <v>90407</v>
       </c>
     </row>
     <row r="185">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>98969</v>
+        <v>93777</v>
       </c>
       <c r="D185" t="n">
         <v>191890</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D186" t="n">
         <v>191890</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>98969</v>
+        <v>93777</v>
       </c>
       <c r="D187" t="n">
-        <v>99580</v>
+        <v>94387</v>
       </c>
     </row>
     <row r="188">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>102038</v>
+        <v>100217</v>
       </c>
       <c r="D188" t="n">
         <v>198135</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D189" t="n">
         <v>198135</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>102038</v>
+        <v>100217</v>
       </c>
       <c r="D190" t="n">
-        <v>102661</v>
+        <v>100843</v>
       </c>
     </row>
     <row r="191">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>105008</v>
+        <v>100288</v>
       </c>
       <c r="D191" t="n">
         <v>204480</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D192" t="n">
         <v>204480</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>105008</v>
+        <v>100288</v>
       </c>
       <c r="D193" t="n">
-        <v>105640</v>
+        <v>100923</v>
       </c>
     </row>
     <row r="194">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>104816</v>
+        <v>101580</v>
       </c>
       <c r="D194" t="n">
         <v>210925</v>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D195" t="n">
         <v>210925</v>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>104816</v>
+        <v>101580</v>
       </c>
       <c r="D196" t="n">
-        <v>105461</v>
+        <v>102225</v>
       </c>
     </row>
     <row r="197">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>106470</v>
+        <v>100454</v>
       </c>
       <c r="D197" t="n">
         <v>217470</v>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D198" t="n">
         <v>217470</v>
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>106470</v>
+        <v>100454</v>
       </c>
       <c r="D199" t="n">
-        <v>107123</v>
+        <v>101108</v>
       </c>
     </row>
     <row r="200">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>114160</v>
+        <v>108477</v>
       </c>
       <c r="D200" t="n">
         <v>224115</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D201" t="n">
         <v>224115</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>114160</v>
+        <v>108477</v>
       </c>
       <c r="D202" t="n">
-        <v>114824</v>
+        <v>109139</v>
       </c>
     </row>
     <row r="203">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>120386</v>
+        <v>116885</v>
       </c>
       <c r="D203" t="n">
         <v>230860</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="D204" t="n">
         <v>230860</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>120386</v>
+        <v>116885</v>
       </c>
       <c r="D205" t="n">
-        <v>121057</v>
+        <v>117561</v>
       </c>
     </row>
     <row r="206">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>121037</v>
+        <v>124814</v>
       </c>
       <c r="D206" t="n">
         <v>237705</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D207" t="n">
         <v>237705</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>121037</v>
+        <v>124814</v>
       </c>
       <c r="D208" t="n">
-        <v>121723</v>
+        <v>125497</v>
       </c>
     </row>
     <row r="209">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>120929</v>
+        <v>123931</v>
       </c>
       <c r="D209" t="n">
         <v>244650</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D210" t="n">
         <v>244650</v>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>120929</v>
+        <v>123931</v>
       </c>
       <c r="D211" t="n">
-        <v>121624</v>
+        <v>124623</v>
       </c>
     </row>
     <row r="212">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>129994</v>
+        <v>125764</v>
       </c>
       <c r="D212" t="n">
         <v>251695</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D213" t="n">
         <v>251695</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>129994</v>
+        <v>125764</v>
       </c>
       <c r="D214" t="n">
-        <v>130699</v>
+        <v>126466</v>
       </c>
     </row>
     <row r="215">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>125148</v>
+        <v>125393</v>
       </c>
       <c r="D215" t="n">
         <v>258840</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D216" t="n">
         <v>258840</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>125148</v>
+        <v>125393</v>
       </c>
       <c r="D217" t="n">
-        <v>125861</v>
+        <v>126104</v>
       </c>
     </row>
     <row r="218">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>138438</v>
+        <v>131917</v>
       </c>
       <c r="D218" t="n">
         <v>266085</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D219" t="n">
         <v>266085</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>138438</v>
+        <v>131917</v>
       </c>
       <c r="D220" t="n">
-        <v>139161</v>
+        <v>132642</v>
       </c>
     </row>
     <row r="221">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>133957</v>
+        <v>136610</v>
       </c>
       <c r="D221" t="n">
         <v>273430</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="D222" t="n">
         <v>273430</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>133957</v>
+        <v>136610</v>
       </c>
       <c r="D223" t="n">
-        <v>134692</v>
+        <v>137342</v>
       </c>
     </row>
     <row r="224">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>139646</v>
+        <v>143863</v>
       </c>
       <c r="D224" t="n">
         <v>280875</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D225" t="n">
         <v>280875</v>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>139646</v>
+        <v>143863</v>
       </c>
       <c r="D226" t="n">
-        <v>140393</v>
+        <v>144605</v>
       </c>
     </row>
     <row r="227">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>140892</v>
+        <v>145951</v>
       </c>
       <c r="D227" t="n">
         <v>288420</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D228" t="n">
         <v>288420</v>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>140892</v>
+        <v>145951</v>
       </c>
       <c r="D229" t="n">
-        <v>141642</v>
+        <v>146705</v>
       </c>
     </row>
     <row r="230">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>142504</v>
+        <v>145943</v>
       </c>
       <c r="D230" t="n">
         <v>296065</v>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D231" t="n">
         <v>296065</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>142504</v>
+        <v>145943</v>
       </c>
       <c r="D232" t="n">
-        <v>143264</v>
+        <v>146705</v>
       </c>
     </row>
     <row r="233">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>148810</v>
+        <v>156131</v>
       </c>
       <c r="D233" t="n">
         <v>303810</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D234" t="n">
         <v>303810</v>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>148810</v>
+        <v>156131</v>
       </c>
       <c r="D235" t="n">
-        <v>149584</v>
+        <v>156906</v>
       </c>
     </row>
     <row r="236">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>155336</v>
+        <v>148578</v>
       </c>
       <c r="D236" t="n">
         <v>311655</v>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D237" t="n">
         <v>311655</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>155336</v>
+        <v>148578</v>
       </c>
       <c r="D238" t="n">
-        <v>156116</v>
+        <v>149357</v>
       </c>
     </row>
     <row r="239">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>162342</v>
+        <v>163908</v>
       </c>
       <c r="D239" t="n">
         <v>319600</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D240" t="n">
         <v>319600</v>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>162342</v>
+        <v>163908</v>
       </c>
       <c r="D241" t="n">
-        <v>163136</v>
+        <v>164702</v>
       </c>
     </row>
     <row r="242">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>162481</v>
+        <v>163416</v>
       </c>
       <c r="D242" t="n">
         <v>327645</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D243" t="n">
         <v>327645</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>162481</v>
+        <v>163416</v>
       </c>
       <c r="D244" t="n">
-        <v>163285</v>
+        <v>164221</v>
       </c>
     </row>
     <row r="245">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>170223</v>
+        <v>165318</v>
       </c>
       <c r="D245" t="n">
         <v>335790</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D246" t="n">
         <v>335790</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>170223</v>
+        <v>165318</v>
       </c>
       <c r="D247" t="n">
-        <v>171035</v>
+        <v>166134</v>
       </c>
     </row>
     <row r="248">
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>171098</v>
+        <v>172797</v>
       </c>
       <c r="D248" t="n">
         <v>344035</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D249" t="n">
         <v>344035</v>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>171098</v>
+        <v>172797</v>
       </c>
       <c r="D250" t="n">
-        <v>171917</v>
+        <v>173618</v>
       </c>
     </row>
     <row r="251">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>174590</v>
+        <v>180254</v>
       </c>
       <c r="D251" t="n">
         <v>352380</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D252" t="n">
         <v>352380</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>174590</v>
+        <v>180254</v>
       </c>
       <c r="D253" t="n">
-        <v>175425</v>
+        <v>181088</v>
       </c>
     </row>
     <row r="254">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>175380</v>
+        <v>178698</v>
       </c>
       <c r="D254" t="n">
         <v>360825</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D255" t="n">
         <v>360825</v>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>175380</v>
+        <v>178698</v>
       </c>
       <c r="D256" t="n">
-        <v>176221</v>
+        <v>179540</v>
       </c>
     </row>
     <row r="257">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>191557</v>
+        <v>192230</v>
       </c>
       <c r="D257" t="n">
         <v>369370</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D258" t="n">
         <v>369370</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>191557</v>
+        <v>192230</v>
       </c>
       <c r="D259" t="n">
-        <v>192412</v>
+        <v>193085</v>
       </c>
     </row>
     <row r="260">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>188272</v>
+        <v>192591</v>
       </c>
       <c r="D260" t="n">
         <v>378015</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D261" t="n">
         <v>378015</v>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>188272</v>
+        <v>192591</v>
       </c>
       <c r="D262" t="n">
-        <v>189138</v>
+        <v>193455</v>
       </c>
     </row>
     <row r="263">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>195328</v>
+        <v>191604</v>
       </c>
       <c r="D263" t="n">
         <v>386760</v>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D264" t="n">
         <v>386760</v>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>195328</v>
+        <v>191604</v>
       </c>
       <c r="D265" t="n">
-        <v>196198</v>
+        <v>192473</v>
       </c>
     </row>
     <row r="266">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>199641</v>
+        <v>200498</v>
       </c>
       <c r="D266" t="n">
         <v>395605</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D267" t="n">
         <v>395605</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>199641</v>
+        <v>200498</v>
       </c>
       <c r="D268" t="n">
-        <v>200526</v>
+        <v>201383</v>
       </c>
     </row>
     <row r="269">
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>199248</v>
+        <v>202781</v>
       </c>
       <c r="D269" t="n">
         <v>404550</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D270" t="n">
         <v>404550</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>199248</v>
+        <v>202781</v>
       </c>
       <c r="D271" t="n">
-        <v>200144</v>
+        <v>203673</v>
       </c>
     </row>
     <row r="272">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>201234</v>
+        <v>208278</v>
       </c>
       <c r="D272" t="n">
         <v>413595</v>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D273" t="n">
         <v>413595</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>201234</v>
+        <v>208278</v>
       </c>
       <c r="D274" t="n">
-        <v>202133</v>
+        <v>209184</v>
       </c>
     </row>
     <row r="275">
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>201878</v>
+        <v>203659</v>
       </c>
       <c r="D275" t="n">
         <v>422740</v>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D276" t="n">
         <v>422740</v>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>201878</v>
+        <v>203659</v>
       </c>
       <c r="D277" t="n">
-        <v>202791</v>
+        <v>204570</v>
       </c>
     </row>
     <row r="278">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>216216</v>
+        <v>210870</v>
       </c>
       <c r="D278" t="n">
         <v>431985</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D279" t="n">
         <v>431985</v>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>216216</v>
+        <v>210870</v>
       </c>
       <c r="D280" t="n">
-        <v>217140</v>
+        <v>211791</v>
       </c>
     </row>
     <row r="281">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>229220</v>
+        <v>222954</v>
       </c>
       <c r="D281" t="n">
         <v>441330</v>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="D282" t="n">
         <v>441330</v>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>229220</v>
+        <v>222954</v>
       </c>
       <c r="D283" t="n">
-        <v>230151</v>
+        <v>223885</v>
       </c>
     </row>
     <row r="284">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>228335</v>
+        <v>220738</v>
       </c>
       <c r="D284" t="n">
         <v>450775</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>228335</v>
+        <v>220738</v>
       </c>
       <c r="D286" t="n">
-        <v>229275</v>
+        <v>221678</v>
       </c>
     </row>
     <row r="287">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>230734</v>
+        <v>231590</v>
       </c>
       <c r="D287" t="n">
         <v>460320</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>230734</v>
+        <v>231590</v>
       </c>
       <c r="D289" t="n">
-        <v>231687</v>
+        <v>232542</v>
       </c>
     </row>
     <row r="290">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>240940</v>
+        <v>236926</v>
       </c>
       <c r="D290" t="n">
         <v>469965</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>240940</v>
+        <v>236926</v>
       </c>
       <c r="D292" t="n">
-        <v>241903</v>
+        <v>237892</v>
       </c>
     </row>
     <row r="293">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>249649</v>
+        <v>230581</v>
       </c>
       <c r="D293" t="n">
         <v>479710</v>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D294" t="n">
         <v>479710</v>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>249649</v>
+        <v>230581</v>
       </c>
       <c r="D295" t="n">
-        <v>250623</v>
+        <v>231554</v>
       </c>
     </row>
     <row r="296">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>237734</v>
+        <v>234752</v>
       </c>
       <c r="D296" t="n">
         <v>489555</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D297" t="n">
         <v>489555</v>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>237734</v>
+        <v>234752</v>
       </c>
       <c r="D298" t="n">
-        <v>238715</v>
+        <v>235737</v>
       </c>
     </row>
     <row r="299">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>255369</v>
+        <v>242629</v>
       </c>
       <c r="D299" t="n">
         <v>499500</v>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>255369</v>
+        <v>242629</v>
       </c>
       <c r="D301" t="n">
-        <v>256362</v>
+        <v>243617</v>
       </c>
     </row>
   </sheetData>

--- a/dsa_py/SortingAnalysis.xlsx
+++ b/dsa_py/SortingAnalysis.xlsx
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
         <v>45</v>
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>45</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D5" t="n">
         <v>190</v>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>190</v>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>97</v>
+      </c>
+      <c r="D7" t="n">
         <v>112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="D8" t="n">
         <v>435</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>363</v>
+        <v>488</v>
       </c>
       <c r="D11" t="n">
         <v>780</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
         <v>780</v>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>363</v>
+        <v>488</v>
       </c>
       <c r="D13" t="n">
-        <v>398</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>678</v>
+        <v>616</v>
       </c>
       <c r="D14" t="n">
         <v>1225</v>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
         <v>1225</v>
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>678</v>
+        <v>616</v>
       </c>
       <c r="D16" t="n">
-        <v>722</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>998</v>
+        <v>971</v>
       </c>
       <c r="D17" t="n">
         <v>1770</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>1770</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>998</v>
+        <v>971</v>
       </c>
       <c r="D19" t="n">
-        <v>1051</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1401</v>
+        <v>1313</v>
       </c>
       <c r="D20" t="n">
         <v>2415</v>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
         <v>2415</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1401</v>
+        <v>1313</v>
       </c>
       <c r="D22" t="n">
-        <v>1468</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="23">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1464</v>
+        <v>1623</v>
       </c>
       <c r="D23" t="n">
         <v>3160</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D24" t="n">
         <v>3160</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1464</v>
+        <v>1623</v>
       </c>
       <c r="D25" t="n">
-        <v>1539</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="26">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2306</v>
+        <v>2089</v>
       </c>
       <c r="D26" t="n">
         <v>4005</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D27" t="n">
         <v>4005</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2306</v>
+        <v>2089</v>
       </c>
       <c r="D28" t="n">
-        <v>2391</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="29">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2185</v>
+        <v>2494</v>
       </c>
       <c r="D29" t="n">
         <v>4950</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D30" t="n">
         <v>4950</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2185</v>
+        <v>2494</v>
       </c>
       <c r="D31" t="n">
-        <v>2281</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="32">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3472</v>
+        <v>3321</v>
       </c>
       <c r="D32" t="n">
         <v>5995</v>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" t="n">
         <v>5995</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3472</v>
+        <v>3321</v>
       </c>
       <c r="D34" t="n">
-        <v>3576</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="35">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4148</v>
+        <v>3020</v>
       </c>
       <c r="D35" t="n">
         <v>7140</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4148</v>
+        <v>3020</v>
       </c>
       <c r="D37" t="n">
-        <v>4262</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="38">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3816</v>
+        <v>4068</v>
       </c>
       <c r="D38" t="n">
         <v>8385</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D39" t="n">
         <v>8385</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3816</v>
+        <v>4068</v>
       </c>
       <c r="D40" t="n">
-        <v>3940</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="41">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5128</v>
+        <v>5012</v>
       </c>
       <c r="D41" t="n">
         <v>9730</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D42" t="n">
         <v>9730</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5128</v>
+        <v>5012</v>
       </c>
       <c r="D43" t="n">
-        <v>5259</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="44">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5844</v>
+        <v>5800</v>
       </c>
       <c r="D44" t="n">
         <v>11175</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5844</v>
+        <v>5800</v>
       </c>
       <c r="D46" t="n">
-        <v>5990</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="47">
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6677</v>
+        <v>6998</v>
       </c>
       <c r="D47" t="n">
         <v>12720</v>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D48" t="n">
         <v>12720</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6677</v>
+        <v>6998</v>
       </c>
       <c r="D49" t="n">
-        <v>6831</v>
+        <v>7154</v>
       </c>
     </row>
     <row r="50">
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6915</v>
+        <v>7216</v>
       </c>
       <c r="D50" t="n">
         <v>14365</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D51" t="n">
         <v>14365</v>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6915</v>
+        <v>7216</v>
       </c>
       <c r="D52" t="n">
-        <v>7079</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="53">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7752</v>
+        <v>6944</v>
       </c>
       <c r="D53" t="n">
         <v>16110</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D54" t="n">
         <v>16110</v>
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7752</v>
+        <v>6944</v>
       </c>
       <c r="D55" t="n">
-        <v>7928</v>
+        <v>7114</v>
       </c>
     </row>
     <row r="56">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9320</v>
+        <v>9299</v>
       </c>
       <c r="D56" t="n">
         <v>17955</v>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D57" t="n">
         <v>17955</v>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9320</v>
+        <v>9299</v>
       </c>
       <c r="D58" t="n">
-        <v>9504</v>
+        <v>9485</v>
       </c>
     </row>
     <row r="59">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9900</v>
+        <v>9620</v>
       </c>
       <c r="D59" t="n">
         <v>19900</v>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D60" t="n">
         <v>19900</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9900</v>
+        <v>9620</v>
       </c>
       <c r="D61" t="n">
-        <v>10093</v>
+        <v>9816</v>
       </c>
     </row>
     <row r="62">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10627</v>
+        <v>10616</v>
       </c>
       <c r="D62" t="n">
         <v>21945</v>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D63" t="n">
         <v>21945</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10627</v>
+        <v>10616</v>
       </c>
       <c r="D64" t="n">
-        <v>10835</v>
+        <v>10819</v>
       </c>
     </row>
     <row r="65">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>12430</v>
+        <v>10860</v>
       </c>
       <c r="D65" t="n">
         <v>24090</v>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D66" t="n">
         <v>24090</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12430</v>
+        <v>10860</v>
       </c>
       <c r="D67" t="n">
-        <v>12642</v>
+        <v>11071</v>
       </c>
     </row>
     <row r="68">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13808</v>
+        <v>12697</v>
       </c>
       <c r="D68" t="n">
         <v>26335</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D69" t="n">
         <v>26335</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>13808</v>
+        <v>12697</v>
       </c>
       <c r="D70" t="n">
-        <v>14032</v>
+        <v>12919</v>
       </c>
     </row>
     <row r="71">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>13667</v>
+        <v>14251</v>
       </c>
       <c r="D71" t="n">
         <v>28680</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13667</v>
+        <v>14251</v>
       </c>
       <c r="D73" t="n">
-        <v>13905</v>
+        <v>14487</v>
       </c>
     </row>
     <row r="74">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>15888</v>
+        <v>15119</v>
       </c>
       <c r="D74" t="n">
         <v>31125</v>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D75" t="n">
         <v>31125</v>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15888</v>
+        <v>15119</v>
       </c>
       <c r="D76" t="n">
-        <v>16131</v>
+        <v>15364</v>
       </c>
     </row>
     <row r="77">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>17061</v>
+        <v>16447</v>
       </c>
       <c r="D77" t="n">
         <v>33670</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D78" t="n">
         <v>33670</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>17061</v>
+        <v>16447</v>
       </c>
       <c r="D79" t="n">
-        <v>17312</v>
+        <v>16701</v>
       </c>
     </row>
     <row r="80">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>18182</v>
+        <v>18482</v>
       </c>
       <c r="D80" t="n">
         <v>36315</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D81" t="n">
         <v>36315</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>18182</v>
+        <v>18482</v>
       </c>
       <c r="D82" t="n">
-        <v>18446</v>
+        <v>18748</v>
       </c>
     </row>
     <row r="83">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>20393</v>
+        <v>18977</v>
       </c>
       <c r="D83" t="n">
         <v>39060</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D84" t="n">
         <v>39060</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>20393</v>
+        <v>18977</v>
       </c>
       <c r="D85" t="n">
-        <v>20667</v>
+        <v>19250</v>
       </c>
     </row>
     <row r="86">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>20452</v>
+        <v>21493</v>
       </c>
       <c r="D86" t="n">
         <v>41905</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D87" t="n">
         <v>41905</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>20452</v>
+        <v>21493</v>
       </c>
       <c r="D88" t="n">
-        <v>20735</v>
+        <v>21776</v>
       </c>
     </row>
     <row r="89">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>20743</v>
+        <v>21541</v>
       </c>
       <c r="D89" t="n">
         <v>44850</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D90" t="n">
         <v>44850</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>20743</v>
+        <v>21541</v>
       </c>
       <c r="D91" t="n">
-        <v>21036</v>
+        <v>21837</v>
       </c>
     </row>
     <row r="92">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>24222</v>
+        <v>24330</v>
       </c>
       <c r="D92" t="n">
         <v>47895</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D93" t="n">
         <v>47895</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>24222</v>
+        <v>24330</v>
       </c>
       <c r="D94" t="n">
-        <v>24527</v>
+        <v>24631</v>
       </c>
     </row>
     <row r="95">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>24820</v>
+        <v>24752</v>
       </c>
       <c r="D95" t="n">
         <v>51040</v>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D96" t="n">
         <v>51040</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>24820</v>
+        <v>24752</v>
       </c>
       <c r="D97" t="n">
-        <v>25133</v>
+        <v>25067</v>
       </c>
     </row>
     <row r="98">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>28030</v>
+        <v>26771</v>
       </c>
       <c r="D98" t="n">
         <v>54285</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D99" t="n">
         <v>54285</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>28030</v>
+        <v>26771</v>
       </c>
       <c r="D100" t="n">
-        <v>28356</v>
+        <v>27094</v>
       </c>
     </row>
     <row r="101">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>27849</v>
+        <v>27714</v>
       </c>
       <c r="D101" t="n">
         <v>57630</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D102" t="n">
         <v>57630</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>27849</v>
+        <v>27714</v>
       </c>
       <c r="D103" t="n">
-        <v>28185</v>
+        <v>28048</v>
       </c>
     </row>
     <row r="104">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>31976</v>
+        <v>32321</v>
       </c>
       <c r="D104" t="n">
         <v>61075</v>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D105" t="n">
         <v>61075</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>31976</v>
+        <v>32321</v>
       </c>
       <c r="D106" t="n">
-        <v>32322</v>
+        <v>32662</v>
       </c>
     </row>
     <row r="107">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>30731</v>
+        <v>32689</v>
       </c>
       <c r="D107" t="n">
         <v>64620</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D108" t="n">
         <v>64620</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>30731</v>
+        <v>32689</v>
       </c>
       <c r="D109" t="n">
-        <v>31080</v>
+        <v>33039</v>
       </c>
     </row>
     <row r="110">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>35322</v>
+        <v>34670</v>
       </c>
       <c r="D110" t="n">
         <v>68265</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="D111" t="n">
         <v>68265</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>35322</v>
+        <v>34670</v>
       </c>
       <c r="D112" t="n">
-        <v>35684</v>
+        <v>35034</v>
       </c>
     </row>
     <row r="113">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>36502</v>
+        <v>35667</v>
       </c>
       <c r="D113" t="n">
         <v>72010</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D114" t="n">
         <v>72010</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>36502</v>
+        <v>35667</v>
       </c>
       <c r="D115" t="n">
-        <v>36875</v>
+        <v>36038</v>
       </c>
     </row>
     <row r="116">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>36510</v>
+        <v>37908</v>
       </c>
       <c r="D116" t="n">
         <v>75855</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D117" t="n">
         <v>75855</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>36510</v>
+        <v>37908</v>
       </c>
       <c r="D118" t="n">
-        <v>36894</v>
+        <v>38292</v>
       </c>
     </row>
     <row r="119">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>40521</v>
+        <v>39325</v>
       </c>
       <c r="D119" t="n">
         <v>79800</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D120" t="n">
         <v>79800</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>40521</v>
+        <v>39325</v>
       </c>
       <c r="D121" t="n">
-        <v>40914</v>
+        <v>39722</v>
       </c>
     </row>
     <row r="122">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>44440</v>
+        <v>41477</v>
       </c>
       <c r="D122" t="n">
         <v>83845</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D123" t="n">
         <v>83845</v>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>44440</v>
+        <v>41477</v>
       </c>
       <c r="D124" t="n">
-        <v>44843</v>
+        <v>41880</v>
       </c>
     </row>
     <row r="125">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>45085</v>
+        <v>45427</v>
       </c>
       <c r="D125" t="n">
         <v>87990</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D126" t="n">
         <v>87990</v>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>45085</v>
+        <v>45427</v>
       </c>
       <c r="D127" t="n">
-        <v>45498</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="128">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>46441</v>
+        <v>44900</v>
       </c>
       <c r="D128" t="n">
         <v>92235</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D129" t="n">
         <v>92235</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>46441</v>
+        <v>44900</v>
       </c>
       <c r="D130" t="n">
-        <v>46864</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="131">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>46745</v>
+        <v>50103</v>
       </c>
       <c r="D131" t="n">
         <v>96580</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>46745</v>
+        <v>50103</v>
       </c>
       <c r="D133" t="n">
-        <v>47178</v>
+        <v>50538</v>
       </c>
     </row>
     <row r="134">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>52711</v>
+        <v>52294</v>
       </c>
       <c r="D134" t="n">
         <v>101025</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D135" t="n">
         <v>101025</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>52711</v>
+        <v>52294</v>
       </c>
       <c r="D136" t="n">
-        <v>53151</v>
+        <v>52739</v>
       </c>
     </row>
     <row r="137">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>52042</v>
+        <v>50076</v>
       </c>
       <c r="D137" t="n">
         <v>105570</v>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D138" t="n">
         <v>105570</v>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>52042</v>
+        <v>50076</v>
       </c>
       <c r="D139" t="n">
-        <v>52495</v>
+        <v>50534</v>
       </c>
     </row>
     <row r="140">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>53737</v>
+        <v>52937</v>
       </c>
       <c r="D140" t="n">
         <v>110215</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D141" t="n">
         <v>110215</v>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>53737</v>
+        <v>52937</v>
       </c>
       <c r="D142" t="n">
-        <v>54203</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="143">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>55629</v>
+        <v>54449</v>
       </c>
       <c r="D143" t="n">
         <v>114960</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D144" t="n">
         <v>114960</v>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>55629</v>
+        <v>54449</v>
       </c>
       <c r="D145" t="n">
-        <v>56104</v>
+        <v>54922</v>
       </c>
     </row>
     <row r="146">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>59708</v>
+        <v>63181</v>
       </c>
       <c r="D146" t="n">
         <v>119805</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D147" t="n">
         <v>119805</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>59708</v>
+        <v>63181</v>
       </c>
       <c r="D148" t="n">
-        <v>60193</v>
+        <v>63669</v>
       </c>
     </row>
     <row r="149">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>63190</v>
+        <v>64817</v>
       </c>
       <c r="D149" t="n">
         <v>124750</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D150" t="n">
         <v>124750</v>
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>63190</v>
+        <v>64817</v>
       </c>
       <c r="D151" t="n">
-        <v>63682</v>
+        <v>65315</v>
       </c>
     </row>
     <row r="152">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>67043</v>
+        <v>62631</v>
       </c>
       <c r="D152" t="n">
         <v>129795</v>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D153" t="n">
         <v>129795</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>67043</v>
+        <v>62631</v>
       </c>
       <c r="D154" t="n">
-        <v>67545</v>
+        <v>63132</v>
       </c>
     </row>
     <row r="155">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>70385</v>
+        <v>67060</v>
       </c>
       <c r="D155" t="n">
         <v>134940</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D156" t="n">
         <v>134940</v>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>70385</v>
+        <v>67060</v>
       </c>
       <c r="D157" t="n">
-        <v>70896</v>
+        <v>67574</v>
       </c>
     </row>
     <row r="158">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>70192</v>
+        <v>69739</v>
       </c>
       <c r="D158" t="n">
         <v>140185</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D159" t="n">
         <v>140185</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>70192</v>
+        <v>69739</v>
       </c>
       <c r="D160" t="n">
-        <v>70714</v>
+        <v>70262</v>
       </c>
     </row>
     <row r="161">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>71701</v>
+        <v>70117</v>
       </c>
       <c r="D161" t="n">
         <v>145530</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D162" t="n">
         <v>145530</v>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>71701</v>
+        <v>70117</v>
       </c>
       <c r="D163" t="n">
-        <v>72235</v>
+        <v>70649</v>
       </c>
     </row>
     <row r="164">
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>74967</v>
+        <v>74335</v>
       </c>
       <c r="D164" t="n">
         <v>150975</v>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D165" t="n">
         <v>150975</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>74967</v>
+        <v>74335</v>
       </c>
       <c r="D166" t="n">
-        <v>75508</v>
+        <v>74879</v>
       </c>
     </row>
     <row r="167">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>82562</v>
+        <v>81952</v>
       </c>
       <c r="D167" t="n">
         <v>156520</v>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D168" t="n">
         <v>156520</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>82562</v>
+        <v>81952</v>
       </c>
       <c r="D169" t="n">
-        <v>83113</v>
+        <v>82508</v>
       </c>
     </row>
     <row r="170">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>80489</v>
+        <v>82899</v>
       </c>
       <c r="D170" t="n">
         <v>162165</v>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D171" t="n">
         <v>162165</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>80489</v>
+        <v>82899</v>
       </c>
       <c r="D172" t="n">
-        <v>81055</v>
+        <v>83460</v>
       </c>
     </row>
     <row r="173">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>83392</v>
+        <v>80658</v>
       </c>
       <c r="D173" t="n">
         <v>167910</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D174" t="n">
         <v>167910</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>83392</v>
+        <v>80658</v>
       </c>
       <c r="D175" t="n">
-        <v>83967</v>
+        <v>81230</v>
       </c>
     </row>
     <row r="176">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>84767</v>
+        <v>82514</v>
       </c>
       <c r="D176" t="n">
         <v>173755</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D177" t="n">
         <v>173755</v>
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>84767</v>
+        <v>82514</v>
       </c>
       <c r="D178" t="n">
-        <v>85354</v>
+        <v>83098</v>
       </c>
     </row>
     <row r="179">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>88724</v>
+        <v>91119</v>
       </c>
       <c r="D179" t="n">
         <v>179700</v>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D180" t="n">
         <v>179700</v>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>88724</v>
+        <v>91119</v>
       </c>
       <c r="D181" t="n">
-        <v>89321</v>
+        <v>91707</v>
       </c>
     </row>
     <row r="182">
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>89804</v>
+        <v>91790</v>
       </c>
       <c r="D182" t="n">
         <v>185745</v>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D183" t="n">
         <v>185745</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>89804</v>
+        <v>91790</v>
       </c>
       <c r="D184" t="n">
-        <v>90407</v>
+        <v>92393</v>
       </c>
     </row>
     <row r="185">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>93777</v>
+        <v>94271</v>
       </c>
       <c r="D185" t="n">
         <v>191890</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D186" t="n">
         <v>191890</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>93777</v>
+        <v>94271</v>
       </c>
       <c r="D187" t="n">
-        <v>94387</v>
+        <v>94884</v>
       </c>
     </row>
     <row r="188">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>100217</v>
+        <v>101561</v>
       </c>
       <c r="D188" t="n">
         <v>198135</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D189" t="n">
         <v>198135</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>100217</v>
+        <v>101561</v>
       </c>
       <c r="D190" t="n">
-        <v>100843</v>
+        <v>102183</v>
       </c>
     </row>
     <row r="191">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>100288</v>
+        <v>100735</v>
       </c>
       <c r="D191" t="n">
         <v>204480</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D192" t="n">
         <v>204480</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>100288</v>
+        <v>100735</v>
       </c>
       <c r="D193" t="n">
-        <v>100923</v>
+        <v>101369</v>
       </c>
     </row>
     <row r="194">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>101580</v>
+        <v>110129</v>
       </c>
       <c r="D194" t="n">
         <v>210925</v>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D195" t="n">
         <v>210925</v>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>101580</v>
+        <v>110129</v>
       </c>
       <c r="D196" t="n">
-        <v>102225</v>
+        <v>110770</v>
       </c>
     </row>
     <row r="197">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>100454</v>
+        <v>107390</v>
       </c>
       <c r="D197" t="n">
         <v>217470</v>
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>100454</v>
+        <v>107390</v>
       </c>
       <c r="D199" t="n">
-        <v>101108</v>
+        <v>108045</v>
       </c>
     </row>
     <row r="200">
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>108477</v>
+        <v>110635</v>
       </c>
       <c r="D200" t="n">
         <v>224115</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D201" t="n">
         <v>224115</v>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>108477</v>
+        <v>110635</v>
       </c>
       <c r="D202" t="n">
-        <v>109139</v>
+        <v>111297</v>
       </c>
     </row>
     <row r="203">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>116885</v>
+        <v>113928</v>
       </c>
       <c r="D203" t="n">
         <v>230860</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D204" t="n">
         <v>230860</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>116885</v>
+        <v>113928</v>
       </c>
       <c r="D205" t="n">
-        <v>117561</v>
+        <v>114603</v>
       </c>
     </row>
     <row r="206">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>124814</v>
+        <v>116627</v>
       </c>
       <c r="D206" t="n">
         <v>237705</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D207" t="n">
         <v>237705</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>124814</v>
+        <v>116627</v>
       </c>
       <c r="D208" t="n">
-        <v>125497</v>
+        <v>117305</v>
       </c>
     </row>
     <row r="209">
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>123931</v>
+        <v>118436</v>
       </c>
       <c r="D209" t="n">
         <v>244650</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D210" t="n">
         <v>244650</v>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>123931</v>
+        <v>118436</v>
       </c>
       <c r="D211" t="n">
-        <v>124623</v>
+        <v>119132</v>
       </c>
     </row>
     <row r="212">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>125764</v>
+        <v>127779</v>
       </c>
       <c r="D212" t="n">
         <v>251695</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="D213" t="n">
         <v>251695</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>125764</v>
+        <v>127779</v>
       </c>
       <c r="D214" t="n">
-        <v>126466</v>
+        <v>128481</v>
       </c>
     </row>
     <row r="215">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>125393</v>
+        <v>130504</v>
       </c>
       <c r="D215" t="n">
         <v>258840</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D216" t="n">
         <v>258840</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>125393</v>
+        <v>130504</v>
       </c>
       <c r="D217" t="n">
-        <v>126104</v>
+        <v>131221</v>
       </c>
     </row>
     <row r="218">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>131917</v>
+        <v>129859</v>
       </c>
       <c r="D218" t="n">
         <v>266085</v>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D219" t="n">
         <v>266085</v>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>131917</v>
+        <v>129859</v>
       </c>
       <c r="D220" t="n">
-        <v>132642</v>
+        <v>130584</v>
       </c>
     </row>
     <row r="221">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>136610</v>
+        <v>134588</v>
       </c>
       <c r="D221" t="n">
         <v>273430</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D222" t="n">
         <v>273430</v>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>136610</v>
+        <v>134588</v>
       </c>
       <c r="D223" t="n">
-        <v>137342</v>
+        <v>135318</v>
       </c>
     </row>
     <row r="224">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>143863</v>
+        <v>142220</v>
       </c>
       <c r="D224" t="n">
         <v>280875</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D225" t="n">
         <v>280875</v>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>143863</v>
+        <v>142220</v>
       </c>
       <c r="D226" t="n">
-        <v>144605</v>
+        <v>142958</v>
       </c>
     </row>
     <row r="227">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>145951</v>
+        <v>142762</v>
       </c>
       <c r="D227" t="n">
         <v>288420</v>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D228" t="n">
         <v>288420</v>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>145951</v>
+        <v>142762</v>
       </c>
       <c r="D229" t="n">
-        <v>146705</v>
+        <v>143518</v>
       </c>
     </row>
     <row r="230">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>145943</v>
+        <v>150659</v>
       </c>
       <c r="D230" t="n">
         <v>296065</v>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="D231" t="n">
         <v>296065</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>145943</v>
+        <v>150659</v>
       </c>
       <c r="D232" t="n">
-        <v>146705</v>
+        <v>151422</v>
       </c>
     </row>
     <row r="233">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>156131</v>
+        <v>158199</v>
       </c>
       <c r="D233" t="n">
         <v>303810</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D234" t="n">
         <v>303810</v>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>156131</v>
+        <v>158199</v>
       </c>
       <c r="D235" t="n">
-        <v>156906</v>
+        <v>158973</v>
       </c>
     </row>
     <row r="236">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>148578</v>
+        <v>153022</v>
       </c>
       <c r="D236" t="n">
         <v>311655</v>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D237" t="n">
         <v>311655</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>148578</v>
+        <v>153022</v>
       </c>
       <c r="D238" t="n">
-        <v>149357</v>
+        <v>153805</v>
       </c>
     </row>
     <row r="239">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>163908</v>
+        <v>160913</v>
       </c>
       <c r="D239" t="n">
         <v>319600</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D240" t="n">
         <v>319600</v>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>163908</v>
+        <v>160913</v>
       </c>
       <c r="D241" t="n">
-        <v>164702</v>
+        <v>161704</v>
       </c>
     </row>
     <row r="242">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>163416</v>
+        <v>163739</v>
       </c>
       <c r="D242" t="n">
         <v>327645</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="D243" t="n">
         <v>327645</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>163416</v>
+        <v>163739</v>
       </c>
       <c r="D244" t="n">
-        <v>164221</v>
+        <v>164545</v>
       </c>
     </row>
     <row r="245">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>165318</v>
+        <v>169501</v>
       </c>
       <c r="D245" t="n">
         <v>335790</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D246" t="n">
         <v>335790</v>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>165318</v>
+        <v>169501</v>
       </c>
       <c r="D247" t="n">
-        <v>166134</v>
+        <v>170313</v>
       </c>
     </row>
     <row r="248">
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>172797</v>
+        <v>173329</v>
       </c>
       <c r="D248" t="n">
         <v>344035</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D249" t="n">
         <v>344035</v>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>172797</v>
+        <v>173329</v>
       </c>
       <c r="D250" t="n">
-        <v>173618</v>
+        <v>174154</v>
       </c>
     </row>
     <row r="251">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>180254</v>
+        <v>168195</v>
       </c>
       <c r="D251" t="n">
         <v>352380</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D252" t="n">
         <v>352380</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>180254</v>
+        <v>168195</v>
       </c>
       <c r="D253" t="n">
-        <v>181088</v>
+        <v>169025</v>
       </c>
     </row>
     <row r="254">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>178698</v>
+        <v>181073</v>
       </c>
       <c r="D254" t="n">
         <v>360825</v>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D255" t="n">
         <v>360825</v>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>178698</v>
+        <v>181073</v>
       </c>
       <c r="D256" t="n">
-        <v>179540</v>
+        <v>181917</v>
       </c>
     </row>
     <row r="257">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>192230</v>
+        <v>177611</v>
       </c>
       <c r="D257" t="n">
         <v>369370</v>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D258" t="n">
         <v>369370</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>192230</v>
+        <v>177611</v>
       </c>
       <c r="D259" t="n">
-        <v>193085</v>
+        <v>178467</v>
       </c>
     </row>
     <row r="260">
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>192591</v>
+        <v>191903</v>
       </c>
       <c r="D260" t="n">
         <v>378015</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D261" t="n">
         <v>378015</v>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>192591</v>
+        <v>191903</v>
       </c>
       <c r="D262" t="n">
-        <v>193455</v>
+        <v>192763</v>
       </c>
     </row>
     <row r="263">
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>191604</v>
+        <v>190761</v>
       </c>
       <c r="D263" t="n">
         <v>386760</v>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="D264" t="n">
         <v>386760</v>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>191604</v>
+        <v>190761</v>
       </c>
       <c r="D265" t="n">
-        <v>192473</v>
+        <v>191635</v>
       </c>
     </row>
     <row r="266">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>200498</v>
+        <v>203558</v>
       </c>
       <c r="D266" t="n">
         <v>395605</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D267" t="n">
         <v>395605</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>200498</v>
+        <v>203558</v>
       </c>
       <c r="D268" t="n">
-        <v>201383</v>
+        <v>204442</v>
       </c>
     </row>
     <row r="269">
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>202781</v>
+        <v>198410</v>
       </c>
       <c r="D269" t="n">
         <v>404550</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D270" t="n">
         <v>404550</v>
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>202781</v>
+        <v>198410</v>
       </c>
       <c r="D271" t="n">
-        <v>203673</v>
+        <v>199304</v>
       </c>
     </row>
     <row r="272">
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>208278</v>
+        <v>210071</v>
       </c>
       <c r="D272" t="n">
         <v>413595</v>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D273" t="n">
         <v>413595</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>208278</v>
+        <v>210071</v>
       </c>
       <c r="D274" t="n">
-        <v>209184</v>
+        <v>210972</v>
       </c>
     </row>
     <row r="275">
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>203659</v>
+        <v>207265</v>
       </c>
       <c r="D275" t="n">
         <v>422740</v>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="D276" t="n">
         <v>422740</v>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>203659</v>
+        <v>207265</v>
       </c>
       <c r="D277" t="n">
-        <v>204570</v>
+        <v>208181</v>
       </c>
     </row>
     <row r="278">
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>210870</v>
+        <v>214808</v>
       </c>
       <c r="D278" t="n">
         <v>431985</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D279" t="n">
         <v>431985</v>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>210870</v>
+        <v>214808</v>
       </c>
       <c r="D280" t="n">
-        <v>211791</v>
+        <v>215730</v>
       </c>
     </row>
     <row r="281">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>222954</v>
+        <v>213076</v>
       </c>
       <c r="D281" t="n">
         <v>441330</v>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>222954</v>
+        <v>213076</v>
       </c>
       <c r="D283" t="n">
-        <v>223885</v>
+        <v>214010</v>
       </c>
     </row>
     <row r="284">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>220738</v>
+        <v>220956</v>
       </c>
       <c r="D284" t="n">
         <v>450775</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D285" t="n">
         <v>450775</v>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>220738</v>
+        <v>220956</v>
       </c>
       <c r="D286" t="n">
-        <v>221678</v>
+        <v>221898</v>
       </c>
     </row>
     <row r="287">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>231590</v>
+        <v>232105</v>
       </c>
       <c r="D287" t="n">
         <v>460320</v>
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D288" t="n">
         <v>460320</v>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>231590</v>
+        <v>232105</v>
       </c>
       <c r="D289" t="n">
-        <v>232542</v>
+        <v>233058</v>
       </c>
     </row>
     <row r="290">
@@ -5056,7 +5056,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>236926</v>
+        <v>229545</v>
       </c>
       <c r="D290" t="n">
         <v>469965</v>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D291" t="n">
         <v>469965</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>236926</v>
+        <v>229545</v>
       </c>
       <c r="D292" t="n">
-        <v>237892</v>
+        <v>230508</v>
       </c>
     </row>
     <row r="293">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>230581</v>
+        <v>243495</v>
       </c>
       <c r="D293" t="n">
         <v>479710</v>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>230581</v>
+        <v>243495</v>
       </c>
       <c r="D295" t="n">
-        <v>231554</v>
+        <v>244469</v>
       </c>
     </row>
     <row r="296">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>234752</v>
+        <v>249549</v>
       </c>
       <c r="D296" t="n">
         <v>489555</v>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D297" t="n">
         <v>489555</v>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>234752</v>
+        <v>249549</v>
       </c>
       <c r="D298" t="n">
-        <v>235737</v>
+        <v>250536</v>
       </c>
     </row>
     <row r="299">
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>242629</v>
+        <v>239282</v>
       </c>
       <c r="D299" t="n">
         <v>499500</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D300" t="n">
         <v>499500</v>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>242629</v>
+        <v>239282</v>
       </c>
       <c r="D301" t="n">
-        <v>243617</v>
+        <v>240277</v>
       </c>
     </row>
   </sheetData>
